--- a/02_加值成品/八上/八上3-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上3-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上3-1 波的傳播　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上3-1 波的傳播　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>波傳遞的是什麼？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>縱波</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>頻率</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>原地上下起伏</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>能量</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>非物質</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>振動垂直傳播方向的波是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>介質</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>橫波</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>如繩波</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>振動平行傳播方向的波是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>v=fλ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>頻率</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>縱波</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>如聲波</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>相鄰兩波峰的距離是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>頻率與波長</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>v=fλ</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>波長</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>縱波</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>λ</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>每秒振動次數是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>頻率</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>振幅</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>v=fλ</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>單位Hz</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>波速公式是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>頻率與波長</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>波長</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>P波</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>v=fλ</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>頻率×波長</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>聲波是橫波還是縱波？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>波長</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>頻率</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>縱波</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>疏密傳遞</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>振動最大偏移量是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>頻率</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>振幅</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>頻率與波長</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>v=fλ</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>與能量有關</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>波峰與波谷的最大高度差反映？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>橫波</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>v=fλ</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>波長</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>振幅</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>振幅</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>橫波與縱波都傳遞？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>波速固定</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>能量</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>頻率</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>P波</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>能量</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上3-1 波的傳播　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上3-1 波的傳播　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>頻率2Hz、波長3m，波速？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>4 m</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>6 m/s</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>5 m</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>34 m</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>2×3</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>波速20m/s、頻率5Hz，波長？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>34 m</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>6 m/s</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>T=1/f</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>4 m</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>20/5</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>頻率4Hz的週期是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2 Hz</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>6 m/s</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>0.25 s</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>5 m</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>1/4</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>繩波屬橫波還是縱波？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>波長</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>介質</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>橫波</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>縱波</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>振動⊥</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>波速由什麼決定？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>介質</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>半波長</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>頻率</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>原地上下起伏</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>非頻率</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>週期0.5s的頻率？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>T=1/f</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>0.25 s</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>10 m/s</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>2 Hz</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>1/0.5</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>彈簧疏密波是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>波長</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>縱波</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>波速固定</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>振動∥</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>波速固定時頻率↑波長？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>橫波</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>P波</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>頻率與波長</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>反比</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>頻率5Hz波長2m波速？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>10 m/s</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>5 m</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>4 m</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>34 m</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>5×2</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>波速30m/s頻率6Hz波長？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>5 m</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>2 Hz</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>10 m/s</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>4 m</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>30/6</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上3-1 波的傳播　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上3-1 波的傳播　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何說波不搬運介質？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>振幅</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>波長</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>介質原地振動只傳能量</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>本質</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>地震P波與S波何者為縱波？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>振幅</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>P波</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>疏密縱波</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>同一繩上改變抖動快慢改變什麼？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>v=fλ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>波長</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>橫波</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>頻率與波長</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>波速不變</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>頻率10Hz波速340m/s，波長？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>6 m/s</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>5 m</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>0.25 s</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>34 m</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>340/10</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>振幅加倍波長變嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>波長</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>頻率</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>縱波</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>兩者獨立</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>波從一介質進另一介質，何者不變？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>縱波</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>頻率</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>由波源決定</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>週期與頻率關係？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>5 m</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>T=1/f</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>10 m/s</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>0.25 s</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>倒數</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>波峰到相鄰波谷距離是幾波長？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>頻率與波長</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>半波長</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>橫波</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>λ/2</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>水波中漂浮的葉子如何運動？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>原地上下起伏</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>縱波</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>半波長</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>原地</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>頻率越高波長越短是在什麼固定下？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>介質</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>橫波</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>波速固定</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>反比</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上3-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上3-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>非物質</t>
+          <t>非物質：波在傳遞時，介質本身只是原地振動，真正傳送出去的是能量，不是物質本身</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>如繩波</t>
+          <t>如繩波：振動方向和波前進方向互相垂直的波稱為橫波，例如抖動繩子產生的波</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>如聲波</t>
+          <t>如聲波：振動方向和波前進方向互相平行(同一直線)的波稱為縱波，例如聲波</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>λ</t>
+          <t>λ：波形上重複出現一次的長度叫波長，也就是相鄰兩個波峰之間的距離</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>單位Hz</t>
+          <t>單位Hz：物體每秒振動的次數稱為頻率，單位是赫茲(Hz)</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>頻率×波長</t>
+          <t>頻率×波長：波速的計算公式是波速等於頻率乘以波長，寫作v=fλ</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>疏密傳遞</t>
+          <t>疏密傳遞：聲波是靠介質分子一疏一密振動來傳遞的，振動方向和傳播方向平行，屬於縱波</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>與能量有關</t>
+          <t>與能量有關：振動偏離平衡位置的最大距離稱為振幅，振幅越大，波攜帶的能量通常越大</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>振幅</t>
+          <t>振幅：波峰(或波谷)到平衡位置的最大距離稱為振幅，振幅越大代表波動的能量通常越大</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>能量</t>
+          <t>能量：不論是振動方向與傳播方向垂直的橫波，或方向相同的縱波，波在傳遞過程中主要傳遞的是能量，介質本身不會隨波跑走</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>2×3</t>
+          <t>2×3：波速=頻率×波長，2Hz乘以3公尺等於6公尺/秒</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>20/5</t>
+          <t>20/5：波長=波速÷頻率，20公尺/秒除以5Hz等於4公尺</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>1/4：週期是頻率的倒數，1秒振動4次，每次振動花費1÷4=0.25秒</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>振動⊥</t>
+          <t>振動⊥：抖動繩子時，繩子上下振動，波卻沿繩子水平前進，振動方向和傳播方向垂直，屬於橫波</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>非頻率</t>
+          <t>非頻率：波在介質中傳播的速度主要由介質本身的性質(如密度、彈性)決定，而不是由波源振動的頻率決定</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>1/0.5</t>
+          <t>1/0.5：頻率是週期的倒數，1除以0.5秒等於2赫茲</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>振動∥</t>
+          <t>振動∥：把彈簧一端前後推拉，會看到彈簧圈一疏一密地傳遞，振動方向和波前進方向平行，屬於縱波</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>反比</t>
+          <t>反比：波速=頻率×波長，波速保持固定時，頻率和波長成反比，頻率越高波長就越短</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>5×2</t>
+          <t>5×2：波速=頻率×波長，5赫茲乘以2公尺等於10公尺/秒</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>30/6</t>
+          <t>30/6：波長=波速÷頻率，30公尺/秒除以6赫茲等於5公尺</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>本質</t>
+          <t>本質：波傳遞時，介質中的每個質點只在原地做振動，並不會跟著波一起移動到遠方，真正被傳送出去的只有能量</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>疏密縱波</t>
+          <t>疏密縱波：地震的P波振動方向和傳播方向平行，屬於疏密相間的縱波，傳播速度比横波(S波)快</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>波速不變</t>
+          <t>波速不變：在同一條繩子(同一介質)上，波速由介質本身決定不會變，改變抖動快慢只會改變頻率，波長也會跟著反向改變以維持波速不變</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>340/10</t>
+          <t>340/10：波長=波速÷頻率，340公尺/秒除以10赫茲等於34公尺</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>兩者獨立</t>
+          <t>兩者獨立：振幅代表振動的最大偏移量、和能量有關；波長是由頻率與波速決定的，兩者是各自獨立的物理量，振幅改變不會影響波長</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>由波源決定</t>
+          <t>由波源決定：波的頻率是由波源振動的快慢決定的，即使波從一種介質進入另一種介質、波速和波長跟著改變，頻率仍然維持不變</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>倒數</t>
+          <t>倒數：週期和頻率互為倒數關係，週期T等於1除以頻率f</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>λ/2</t>
+          <t>λ/2：一個完整波長是波峰到下一個波峰，波峰到相鄰波谷只走了一半，所以是半波長</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>原地</t>
+          <t>原地：水波傳遞時，水面上的葉子只會隨著波形在原地上下起伏振動，並不會跟著波一起往前移動，真正傳遞出去的是能量</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>反比</t>
+          <t>反比：波速=頻率×波長，如果波速保持固定不變，頻率和波長就會成反比關係，頻率越高、波長就越短</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上3-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上3-1_三種難度測驗卷.xlsx
@@ -683,12 +683,12 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>頻率與波長</t>
+          <t>振幅</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>v=fλ</t>
+          <t>縱波</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>縱波</t>
+          <t>能量</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -733,12 +733,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>v=fλ</t>
+          <t>P波</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>能量</t>
+          <t>橫波</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>34 m</t>
+          <t>2 Hz</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>6 m/s</t>
+          <t>10 m/s</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1515,17 +1515,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>振幅</t>
+          <t>頻率與波長</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>波長</t>
+          <t>0.25 s</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>能量</t>
+          <t>10 m/s</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>v=fλ</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>波長</t>
+          <t>不變</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>橫波</t>
+          <t>振幅</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>6 m/s</t>
+          <t>0.25 s</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>5 m</t>
+          <t>10 m/s</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>0.25 s</t>
+          <t>2 Hz</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>縱波</t>
+          <t>P波</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>不變</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>能量</t>
+          <t>波速固定</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>頻率與波長</t>
+          <t>不變</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>橫波</t>
+          <t>P波</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>原地上下起伏</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
